--- a/Result/profitability/6515.xlsx
+++ b/Result/profitability/6515.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM35"/>
+  <dimension ref="A1:AM36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4875,6 +4875,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3523</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2173</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1350</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="G36" t="n">
+        <v>825</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>23.42%</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>22</v>
+      </c>
+      <c r="J36" t="n">
+        <v>848</v>
+      </c>
+      <c r="K36" t="n">
+        <v>672</v>
+      </c>
+      <c r="L36" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="M36" t="n">
+        <v>13.41</v>
+      </c>
+      <c r="N36" t="n">
+        <v>43.96749999999999</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W36" t="n">
+        <v>-0.8399999999999999</v>
+      </c>
+      <c r="X36" t="n">
+        <v>-0.04298874104401229</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-0.1088119042083237</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>2.246527777777778</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>-10.64</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>-0.2172758831937921</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK36" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
